--- a/hardware/LM4041 Voltage Reference Design.xlsx
+++ b/hardware/LM4041 Voltage Reference Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aura\Documents\fall25\ece346d-intro_engineering_design\senior-design-strength-training\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84607B49-0478-4CAD-B6AA-771803509E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1523B2AA-AF2D-480C-A524-B95B39514D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
